--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
   <si>
     <t>Filename</t>
   </si>
@@ -808,679 +808,670 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9925,0.0008,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.9964,0.0014,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.1457,0.0001,0.0006,0.9508</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9945,0.0005,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0008,0.9993</t>
+  </si>
+  <si>
+    <t>0.9799,0.0058,0.0005,0.0032</t>
+  </si>
+  <si>
+    <t>0.0772,0.0000,0.0002,0.9809</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9182,0.0025,0.0754,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0010,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.9019,0.0005,0.1459,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0004,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.2586,0.7934,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9781,0.0007,0.0143,0.0001</t>
+  </si>
+  <si>
+    <t>0.9650,0.0005,0.0309,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0009,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.0381,0.0006,0.9762,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.6182,0.2639,0.0135,0.0001</t>
+  </si>
+  <si>
+    <t>0.6941,0.0216,0.1743,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9998,0.0020</t>
+  </si>
+  <si>
+    <t>0.0029,0.9936,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.9789,0.0151,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.0096,0.0094,0.9889,0.0022</t>
+  </si>
+  <si>
+    <t>0.4291,0.6597,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.0090,0.9824,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.6232,0.8054,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0015,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0108,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9986,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0007,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.9498,0.0151,0.1892</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0917,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0089,0.0074,0.9839,0.0044</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.0008,0.9930,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0005,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0014,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0028,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0011,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9784,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0036,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9953,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.9948,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0517,0.0034,0.9623,0.0001</t>
+  </si>
+  <si>
+    <t>0.8464,0.0166,0.1087,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9937,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9723,0.0000</t>
+  </si>
+  <si>
+    <t>0.0049,0.0002,0.0527,0.9873</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.0035,0.9993</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.0004,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9943,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9633,0.9914,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9328,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9629,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9782,0.9849,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0043,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0229,0.0008,0.9882,0.0000</t>
+  </si>
+  <si>
+    <t>0.9941,0.0003,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9994,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9983,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.9951,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.4806,0.5884,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.8044,0.0017,0.2079,0.0002</t>
+  </si>
+  <si>
+    <t>0.8217,0.0003,0.2393,0.0001</t>
+  </si>
+  <si>
+    <t>0.7840,0.0170,0.1365,0.0004</t>
+  </si>
+  <si>
+    <t>0.7369,0.0061,0.2037,0.0010</t>
+  </si>
+  <si>
+    <t>0.0119,0.0669,0.1050,0.6946</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.7093,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9771,0.0120,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.7801,0.2088,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
     <t>0.9995,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0019,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.5055,0.0048,0.5235,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0208,0.9947,0.0007</t>
-  </si>
-  <si>
-    <t>0.9115,0.0010,0.1043,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0002,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.3327,0.7133,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8015,0.0004,0.2675,0.0001</t>
-  </si>
-  <si>
-    <t>0.6072,0.0028,0.4664,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0043,0.9921,0.0008</t>
-  </si>
-  <si>
-    <t>0.0106,0.0001,0.9934,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.3022,0.5776,0.0148,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0012,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0008</t>
-  </si>
-  <si>
-    <t>0.0411,0.7964,0.0468,0.0000</t>
-  </si>
-  <si>
-    <t>0.9756,0.0181,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.9923,0.0035,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0485,0.9410,0.0079,0.0004</t>
-  </si>
-  <si>
-    <t>0.0046,0.9859,0.0266,0.0003</t>
-  </si>
-  <si>
-    <t>0.0309,0.2435,0.5955,0.0035</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0044,0.0032,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0047,0.0001,0.9934,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.2435,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0081,0.0496,0.8695,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0536,0.6689,0.0935,0.0905</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.4871,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0011,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0055,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0015,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.9969,0.0009,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9961,0.9860,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0006,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9822,0.0026,0.0120,0.0000</t>
-  </si>
-  <si>
-    <t>0.9797,0.0027,0.0116,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9922,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9877,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9300,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9941,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0001,0.0081,0.9952</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.0011,0.9995</t>
-  </si>
-  <si>
-    <t>0.0023,0.0002,0.0009,0.9983</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.9114,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9947,0.9433,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9865,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9888,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9866,0.9839,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0018,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
+    <t>0.9983,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.5699,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.4011,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9811,0.0016,0.0130,0.0001</t>
+  </si>
+  <si>
+    <t>0.0518,0.0002,0.9712,0.0000</t>
+  </si>
+  <si>
+    <t>0.9689,0.0008,0.0225,0.0001</t>
+  </si>
+  <si>
+    <t>0.4711,0.0001,0.0003,0.7602</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9949,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0141,0.9785,0.0032,0.0036</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.3165,0.6713,0.0100,0.0008</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0353,0.0000,0.0014,0.9751</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0815,0.9963,0.0004</t>
+  </si>
+  <si>
+    <t>0.9443,0.0001,0.0202,0.0041</t>
+  </si>
+  <si>
+    <t>0.9910,0.0017,0.0038,0.0007</t>
+  </si>
+  <si>
+    <t>0.5892,0.2652,0.0174,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0005,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.9873,0.0057,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.0432,0.9611,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9547,0.0047,0.0305,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0015,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8182,0.2796,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.7082,0.3204,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.8082,0.1509,0.0095,0.0001</t>
+  </si>
+  <si>
+    <t>0.0106,0.0546,0.9792,0.0020</t>
+  </si>
+  <si>
+    <t>0.9964,0.0025,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0016,0.0029,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.8307,0.2853,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9901,0.0019,0.0039,0.0006</t>
+  </si>
+  <si>
+    <t>0.0029,0.0120,0.9897,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0023,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0305,0.0340,0.8640,0.0021</t>
+  </si>
+  <si>
+    <t>0.1837,0.0015,0.8534,0.0001</t>
+  </si>
+  <si>
+    <t>0.0161,0.0080,0.9655,0.0005</t>
+  </si>
+  <si>
+    <t>0.0134,0.0035,0.9876,0.0000</t>
+  </si>
+  <si>
+    <t>0.0252,0.0081,0.9475,0.0005</t>
+  </si>
+  <si>
+    <t>0.7507,0.0014,0.3036,0.0000</t>
+  </si>
+  <si>
+    <t>0.7131,0.0235,0.1765,0.0008</t>
+  </si>
+  <si>
+    <t>0.3677,0.0090,0.6101,0.0005</t>
+  </si>
+  <si>
+    <t>0.0891,0.9379,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.9961,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.5451,0.5547,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.8703,0.2103,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9976,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9508,0.0214,0.0081,0.0004</t>
+  </si>
+  <si>
+    <t>0.9887,0.0004,0.0070,0.0001</t>
+  </si>
+  <si>
+    <t>0.9931,0.0004,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.3263,0.0005,0.7769,0.0001</t>
+  </si>
+  <si>
+    <t>0.3733,0.0007,0.7395,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.0214,0.9878,0.0036</t>
+  </si>
+  <si>
+    <t>0.0007,0.9782,0.4995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0040,0.0002,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0129,0.9987,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0050,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0262,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.1138,0.0363,0.7818,0.0016</t>
+  </si>
+  <si>
+    <t>0.9932,0.0002,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0010,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0203,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0062,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.0042,0.9903,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0366,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.9814,0.0002,0.0168,0.0000</t>
+  </si>
+  <si>
+    <t>0.6757,0.0003,0.4568,0.0001</t>
+  </si>
+  <si>
+    <t>0.9658,0.0002,0.0384,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0027,0.0007,0.0002</t>
   </si>
   <si>
     <t>0.9994,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0096,0.0014,0.9928,0.0001</t>
-  </si>
-  <si>
-    <t>0.9930,0.0001,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.1264,0.0001,0.9316,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9995,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0159,0.9840,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.9949,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7395,0.4021,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.7288,0.0425,0.1110,0.0008</t>
-  </si>
-  <si>
-    <t>0.9641,0.0007,0.0359,0.0000</t>
-  </si>
-  <si>
-    <t>0.2211,0.0528,0.5796,0.0004</t>
-  </si>
-  <si>
-    <t>0.8124,0.0053,0.1537,0.0010</t>
-  </si>
-  <si>
-    <t>0.0018,0.3439,0.0246,0.8212</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.6257,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9972,0.0038,0.0000</t>
-  </si>
-  <si>
-    <t>0.9717,0.0123,0.0089,0.0003</t>
-  </si>
-  <si>
-    <t>0.9367,0.0443,0.0081,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8223,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7668,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0049,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0004,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9293,0.0025,0.0675,0.0003</t>
-  </si>
-  <si>
-    <t>0.6042,0.0002,0.5061,0.0001</t>
-  </si>
-  <si>
-    <t>0.9905,0.0006,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.2746,0.0002,0.0009,0.8682</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0271,0.9698,0.0020,0.0016</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7371,0.3161,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0118,0.0000,0.0037,0.9917</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0406,0.9957,0.0005</t>
-  </si>
-  <si>
-    <t>0.9860,0.0002,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.9967,0.0005,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9138,0.0893,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.9959,0.0007,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9829,0.0096,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.5751,0.4714,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.9658,0.0078,0.0128,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0012,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0009,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.1138,0.9063,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.6486,0.2376,0.0284,0.0002</t>
-  </si>
-  <si>
-    <t>0.9779,0.0125,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.9861,0.0076,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0040,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9884,0.0034,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0019,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0016,0.9942,0.0002</t>
-  </si>
-  <si>
-    <t>0.4793,0.0016,0.5590,0.0003</t>
-  </si>
-  <si>
-    <t>0.0610,0.6748,0.0942,0.0002</t>
-  </si>
-  <si>
-    <t>0.0885,0.0056,0.9218,0.0001</t>
-  </si>
-  <si>
-    <t>0.0379,0.3007,0.5353,0.0002</t>
-  </si>
-  <si>
-    <t>0.2097,0.0052,0.7677,0.0001</t>
-  </si>
-  <si>
-    <t>0.9251,0.0009,0.0775,0.0004</t>
-  </si>
-  <si>
-    <t>0.0465,0.0030,0.9549,0.0003</t>
-  </si>
-  <si>
-    <t>0.0204,0.9807,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0069,0.9934,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.2509,0.7926,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0504,0.9627,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0075,0.9928,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.6965,0.1441,0.0348,0.0004</t>
-  </si>
-  <si>
-    <t>0.9936,0.0001,0.0040,0.0000</t>
-  </si>
-  <si>
-    <t>0.6048,0.0537,0.1383,0.0135</t>
-  </si>
-  <si>
-    <t>0.9034,0.0002,0.1369,0.0000</t>
-  </si>
-  <si>
-    <t>0.6707,0.0010,0.4473,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0006</t>
-  </si>
-  <si>
-    <t>0.0019,0.0211,0.9906,0.0013</t>
-  </si>
-  <si>
-    <t>0.0266,0.0508,0.9182,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0020,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0016,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9960,0.0030,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0044,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.5947,0.0364,0.2269,0.0017</t>
-  </si>
-  <si>
-    <t>0.9909,0.0006,0.0043,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0047,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0222,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0027,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0021,0.9929,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.2052,0.9975,0.0005</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0005,0.0141,0.0001</t>
-  </si>
-  <si>
-    <t>0.9826,0.0001,0.0203,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0072,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0070,0.0040,0.9820,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.3937,0.9703,0.0012</t>
-  </si>
-  <si>
-    <t>0.0239,0.0045,0.9575,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0009,0.9959,0.0023</t>
-  </si>
-  <si>
-    <t>0.3150,0.0011,0.7370,0.0002</t>
-  </si>
-  <si>
-    <t>0.0235,0.0009,0.9651,0.0026</t>
-  </si>
-  <si>
-    <t>0.9821,0.0001,0.0032,0.0059</t>
-  </si>
-  <si>
-    <t>0.0063,0.0151,0.0013,0.9899</t>
-  </si>
-  <si>
-    <t>0.0236,0.0002,0.0044,0.9880</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.9864,0.0019,0.0030,0.0007</t>
+    <t>0.0174,0.0028,0.9757,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0052,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0246,0.9749,0.0014</t>
+  </si>
+  <si>
+    <t>0.0033,0.0034,0.9917,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0036,0.9961,0.0037</t>
+  </si>
+  <si>
+    <t>0.0578,0.0045,0.9409,0.0006</t>
+  </si>
+  <si>
+    <t>0.0043,0.0024,0.9888,0.0021</t>
+  </si>
+  <si>
+    <t>0.9690,0.0000,0.0024,0.0136</t>
+  </si>
+  <si>
+    <t>0.0016,0.0190,0.0002,0.9975</t>
+  </si>
+  <si>
+    <t>0.0167,0.0002,0.0077,0.9893</t>
+  </si>
+  <si>
+    <t>0.6372,0.0506,0.0528,0.0614</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1857,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1871,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1894,7 +1885,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1908,7 +1899,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1922,7 +1913,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1936,7 +1927,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1950,7 +1941,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1964,7 +1955,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1978,7 +1969,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1992,7 +1983,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2006,7 +1997,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2020,7 +2011,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2031,10 +2022,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2048,7 +2039,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2062,7 +2053,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2076,7 +2067,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2090,7 +2081,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2104,7 +2095,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2118,7 +2109,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2132,7 +2123,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2146,7 +2137,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2160,7 +2151,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2174,7 +2165,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2188,7 +2179,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2202,7 +2193,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,7 +2207,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,7 +2221,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2244,7 +2235,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2258,7 +2249,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,10 +2260,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2286,7 +2277,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2300,7 +2291,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,7 +2305,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2328,7 +2319,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2339,10 +2330,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2356,7 +2347,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2370,7 +2361,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2381,10 +2372,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2398,7 +2389,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2412,7 +2403,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2426,7 +2417,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2440,7 +2431,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2451,10 +2442,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2468,7 +2459,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,7 +2473,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2496,7 +2487,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2510,7 +2501,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2524,7 +2515,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2538,7 +2529,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2552,7 +2543,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2566,7 +2557,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2580,7 +2571,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2594,7 +2585,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2608,7 +2599,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2622,7 +2613,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2636,7 +2627,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2650,7 +2641,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2815,7 +2806,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>329</v>
@@ -3084,7 +3075,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3098,7 +3089,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>271</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3112,7 +3103,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3126,7 +3117,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3140,7 +3131,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3154,7 +3145,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3168,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3182,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3196,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3210,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3224,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3238,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3252,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>353</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3266,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3280,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>270</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3294,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3322,7 +3313,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3336,7 +3327,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3350,7 +3341,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3364,7 +3355,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3378,7 +3369,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3392,7 +3383,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3406,7 +3397,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3420,7 +3411,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3434,7 +3425,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,10 +3436,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3462,7 +3453,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3476,7 +3467,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3487,10 +3478,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3504,7 +3495,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3518,7 +3509,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3532,7 +3523,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3546,7 +3537,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>283</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3560,7 +3551,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>308</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3574,7 +3565,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3588,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3602,7 +3593,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,7 +3607,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3630,7 +3621,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3644,7 +3635,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3658,7 +3649,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3672,7 +3663,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3686,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3700,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3714,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3728,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,7 +3733,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3753,10 +3744,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3770,7 +3761,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3784,7 +3775,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3798,7 +3789,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3812,7 +3803,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3826,7 +3817,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3840,7 +3831,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3854,7 +3845,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3868,7 +3859,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3882,7 +3873,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3896,7 +3887,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3910,7 +3901,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3924,7 +3915,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3938,7 +3929,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3952,7 +3943,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3963,10 +3954,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3980,7 +3971,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3994,7 +3985,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4008,7 +3999,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4022,7 +4013,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4036,7 +4027,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4041,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4064,7 +4055,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4078,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4092,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4103,10 +4094,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4120,7 +4111,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4148,7 +4139,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4162,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4176,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4190,7 +4181,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4218,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4232,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4246,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4257,10 +4248,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4274,7 +4265,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4288,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4299,10 +4290,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4316,7 +4307,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4330,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>375</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4344,7 +4335,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4358,7 +4349,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4372,7 +4363,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4386,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4400,7 +4391,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>423</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4414,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4428,7 +4419,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>311</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4442,7 +4433,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4456,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4470,7 +4461,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>326</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4484,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4498,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4512,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4523,10 +4514,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4540,7 +4531,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,7 +4545,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4565,10 +4556,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,7 +4573,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4596,7 +4587,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4610,7 +4601,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4624,7 +4615,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4635,10 +4626,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4649,10 +4640,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4666,7 +4657,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4680,7 +4671,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4694,7 +4685,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4708,7 +4699,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,10 +4710,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,10 +4724,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4750,7 +4741,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4764,7 +4755,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,10 +4766,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4792,7 +4783,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4806,7 +4797,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4820,7 +4811,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4834,7 +4825,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4848,7 +4839,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4862,7 +4853,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>352</v>
+        <v>457</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4876,7 +4867,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4890,7 +4881,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>456</v>
+        <v>381</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4904,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>352</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4918,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>352</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4932,7 +4923,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4943,10 +4934,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4960,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4974,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4988,7 +4979,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5002,7 +4993,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5016,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5030,7 +5021,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5044,7 +5035,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>326</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5128,7 +5119,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>320</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5142,7 +5133,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>320</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5156,7 +5147,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>268</v>
+        <v>352</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5170,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5184,7 +5175,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5198,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5212,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>456</v>
+        <v>270</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5226,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5240,7 +5231,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5254,7 +5245,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5268,7 +5259,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5282,7 +5273,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5296,7 +5287,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5310,7 +5301,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5324,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5338,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,7 +5343,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5366,7 +5357,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5380,7 +5371,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5394,7 +5385,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>487</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5408,7 +5399,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5422,7 +5413,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
